--- a/etc/2026-06.xlsx
+++ b/etc/2026-06.xlsx
@@ -3342,7 +3342,7 @@
         <v>2850.815</v>
       </c>
       <c r="J44" s="6">
-        <v>4845.871</v>
+        <v>5044.04</v>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
@@ -3362,13 +3362,13 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="6">
-        <v>2402.083</v>
+        <v>1681.95</v>
       </c>
       <c r="I45" s="6">
-        <v>2184.077</v>
+        <v>2206.697</v>
       </c>
       <c r="J45" s="6">
-        <v>4771.988</v>
+        <v>2851.616</v>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
